--- a/template.xlsx
+++ b/template.xlsx
@@ -5,16 +5,20 @@
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gorji\source\repos\Osadka\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gorji\source\repos\Osadkaend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500521E3-252D-4CA8-A196-69F67E7AA50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F82F08-AF48-4611-949C-BD045DB69537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Общие" sheetId="1" r:id="rId1"/>
+    <sheet name="Графики динамики" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="DynData" localSheetId="1">'Графики динамики'!$A$1:$C$5</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>Предельная максимальная осадка по СП (мм)</t>
   </si>
@@ -148,6 +152,33 @@
   </si>
   <si>
     <t>/предСПотн</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>25.07.2024г.</t>
+  </si>
+  <si>
+    <t>21.08.2024г.</t>
+  </si>
+  <si>
+    <t>19.09.2024г.</t>
+  </si>
+  <si>
+    <t>22.10.2024г.</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -157,7 +188,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0_ ;\-#,##0.0\ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,6 +202,20 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -214,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -222,6 +267,12 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -232,11 +283,55 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -247,6 +342,1154 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10873928482724826"/>
+          <c:y val="0.10689925215559867"/>
+          <c:w val="0.73139302280309593"/>
+          <c:h val="0.67716989806009487"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Графики динамики'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Графики динамики'!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>25.07.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.08.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.09.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.10.2024г.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Графики динамики'!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-8.6999999999999993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4453-419D-8BFD-96B5689B24B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Графики динамики'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Графики динамики'!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>25.07.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.08.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.09.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.10.2024г.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Графики динамики'!$B$3:$E$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4453-419D-8BFD-96B5689B24B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Графики динамики'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Графики динамики'!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>25.07.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.08.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.09.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.10.2024г.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Графики динамики'!$B$4:$E$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-8.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8543-48D5-B9C9-05537701AD09}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Графики динамики'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Графики динамики'!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>25.07.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.08.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.09.2024г.</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.10.2024г.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Графики динамики'!$B$5:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-8.6999999999999993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EC42-436D-A4AB-558D4C35A4AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1012893727"/>
+        <c:axId val="763184255"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1012893727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="t" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="763184255"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="763184255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1012893727"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.89650468883205459"/>
+          <c:y val="0.38543708003912952"/>
+          <c:w val="7.3657289002557552E-2"/>
+          <c:h val="0.22912583992174099"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5186DFC5-02B5-BFBE-8535-4A8297BF9D69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3CC87B41-D2DD-4B3E-901D-D1DA73A99819}" name="DynTable" displayName="DynTable" ref="A1:E5" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E5" xr:uid="{3CC87B41-D2DD-4B3E-901D-D1DA73A99819}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{6E528EAB-F6A3-4063-BC2F-4E05690C03BE}" name="Id" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{03C31640-2B94-42CD-9E7F-99310E7B3C96}" name="25.07.2024г." dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{D6E533E3-0BE8-49A8-BCC1-850A22494E4B}" name="21.08.2024г." dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{D564C1F9-508E-46CB-9A17-2C83D3C1C848}" name="19.09.2024г." dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{CDB68DB4-80FB-48BE-AAC5-7FB99C974C24}" name="22.10.2024г." dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -526,14 +1769,14 @@
   </cols>
   <sheetData>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C7" s="1"/>
@@ -559,62 +1802,62 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="2" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="10" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -625,7 +1868,7 @@
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -636,7 +1879,7 @@
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -647,14 +1890,14 @@
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="2" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -665,7 +1908,7 @@
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -676,7 +1919,7 @@
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -685,107 +1928,107 @@
       <c r="D22" s="2"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="6"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -816,5 +2059,109 @@
     <mergeCell ref="B37:D37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373D4DE6-5381-4555-9C0C-9DD32DBEEB7F}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>-0.6</v>
+      </c>
+      <c r="D2" s="4">
+        <v>-3.7</v>
+      </c>
+      <c r="E2" s="4">
+        <v>-8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>-0.5</v>
+      </c>
+      <c r="D3" s="4">
+        <v>-3.6</v>
+      </c>
+      <c r="E3" s="4">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>-0.4</v>
+      </c>
+      <c r="D4" s="4">
+        <v>-3.9</v>
+      </c>
+      <c r="E4" s="4">
+        <v>-8.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>-0.5</v>
+      </c>
+      <c r="D5" s="4">
+        <v>-3.3</v>
+      </c>
+      <c r="E5" s="4">
+        <v>-8.6999999999999993</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/template.xlsx
+++ b/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gorji\source\repos\Osadkaend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gorji\source\repos\HorDeform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F82F08-AF48-4611-949C-BD045DB69537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D334EF-D7EE-4EA7-92EF-5F3CD1269455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Общие" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>Предельная максимальная осадка по СП (мм)</t>
   </si>
@@ -46,36 +46,6 @@
     <t>№ марки</t>
   </si>
   <si>
-    <t>Осд. общ макс</t>
-  </si>
-  <si>
-    <t>Осд. общ мин</t>
-  </si>
-  <si>
-    <t>Осд. общ сред</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Осд. за цикл макс</t>
-  </si>
-  <si>
-    <t>Осд. за цикл  мин</t>
-  </si>
-  <si>
-    <t>Осд. за цикл  сред</t>
-  </si>
-  <si>
-    <t>Уничтожены</t>
-  </si>
-  <si>
-    <t>Нет доступа</t>
-  </si>
-  <si>
-    <t>Новые</t>
-  </si>
-  <si>
     <t>Превышения максимальной осадки по СП</t>
   </si>
   <si>
@@ -88,45 +58,6 @@
     <t>Превышения относительной осадки по расчётам</t>
   </si>
   <si>
-    <t>/общмакс</t>
-  </si>
-  <si>
-    <t>/общмаксId</t>
-  </si>
-  <si>
-    <t>/общмин</t>
-  </si>
-  <si>
-    <t>/общминId</t>
-  </si>
-  <si>
-    <t>/общср</t>
-  </si>
-  <si>
-    <t>/сеттмакс</t>
-  </si>
-  <si>
-    <t>/сеттмаксId</t>
-  </si>
-  <si>
-    <t>/сеттмин</t>
-  </si>
-  <si>
-    <t>/сеттминId</t>
-  </si>
-  <si>
-    <t>/сеттср</t>
-  </si>
-  <si>
-    <t>/нетдоступа</t>
-  </si>
-  <si>
-    <t>/уничтожены</t>
-  </si>
-  <si>
-    <t>/новые</t>
-  </si>
-  <si>
     <t>/общ&gt;сп</t>
   </si>
   <si>
@@ -179,16 +110,85 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>/вектормакс</t>
+  </si>
+  <si>
+    <t>/вектормин</t>
+  </si>
+  <si>
+    <t>/вектормаксId</t>
+  </si>
+  <si>
+    <t>/векторминId</t>
+  </si>
+  <si>
+    <t>Вектор Максимум</t>
+  </si>
+  <si>
+    <t>Вектор Минимум</t>
+  </si>
+  <si>
+    <t>ΔX Максимум</t>
+  </si>
+  <si>
+    <t>ΔX Минимум</t>
+  </si>
+  <si>
+    <t>ΔY Максимум</t>
+  </si>
+  <si>
+    <t>ΔY Минимум</t>
+  </si>
+  <si>
+    <t>/дельтаXмакс</t>
+  </si>
+  <si>
+    <t>/дельтаXмин</t>
+  </si>
+  <si>
+    <t>/дельтаYмакс</t>
+  </si>
+  <si>
+    <t>/дельтаYмин</t>
+  </si>
+  <si>
+    <t>ΔH Максимум</t>
+  </si>
+  <si>
+    <t>ΔH Минимум</t>
+  </si>
+  <si>
+    <t>/дельтаHмакс</t>
+  </si>
+  <si>
+    <t>/дельтаHмин</t>
+  </si>
+  <si>
+    <t>/дельтаHмаксId</t>
+  </si>
+  <si>
+    <t>/дельтаHминId</t>
+  </si>
+  <si>
+    <t>/дельтаYмаксId</t>
+  </si>
+  <si>
+    <t>/дельтаYминId</t>
+  </si>
+  <si>
+    <t>/дельтаXмаксId</t>
+  </si>
+  <si>
+    <t>/дельтаXминId</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.0_ ;\-#,##0.0\ "/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,6 +217,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -232,7 +238,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -255,26 +261,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -283,10 +311,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1441,16 +1466,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1769,14 +1794,14 @@
   </cols>
   <sheetData>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C7" s="1"/>
@@ -1802,19 +1827,19 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="B9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="9"/>
-      <c r="D10" s="2" t="s">
-        <v>37</v>
+      <c r="D10" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
@@ -1822,8 +1847,8 @@
         <v>1</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="2" t="s">
-        <v>40</v>
+      <c r="D11" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
@@ -1831,8 +1856,8 @@
         <v>2</v>
       </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="2" t="s">
-        <v>39</v>
+      <c r="D12" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
@@ -1840,204 +1865,201 @@
         <v>3</v>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="10" t="s">
-        <v>4</v>
+      <c r="D19" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>25</v>
+      <c r="B20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>27</v>
+      <c r="B21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="2"/>
+      <c r="B22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="6"/>
+      <c r="B23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="6"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="6"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
+      <c r="B28" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
+      <c r="B31" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="9" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B34" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
+      <c r="B34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="9" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
+      <c r="B37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="21">
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="H6:L6"/>
     <mergeCell ref="B27:D27"/>
@@ -2047,7 +2069,6 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
@@ -2065,96 +2086,236 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373D4DE6-5381-4555-9C0C-9DD32DBEEB7F}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>45</v>
+      <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="4">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2">
         <v>0</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <v>-0.6</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="2">
         <v>-3.7</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="2">
         <v>-8.6999999999999993</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="4">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2">
         <v>0</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>-0.5</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <v>-3.6</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="2">
         <v>-9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2">
         <v>0</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>-0.4</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>-3.9</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>-8.4</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2">
         <v>0</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>-0.5</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>-3.3</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>-8.6999999999999993</v>
       </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="6"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="6"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="7"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="7"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="7"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="7"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="7"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="7"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
